--- a/docs/scientific/quarto-scidoc/data/animal.xlsx
+++ b/docs/scientific/quarto-scidoc/data/animal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gmg228\Documents\RuFaS\RuFaS\docs\scientific\quarto-scidoc\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5929989C-7BDB-4551-9EC3-7AA252BF07AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70555680-4C11-4572-9B02-A6305BE8D36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{F125F8CC-AB11-4532-9330-C9352A35496C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>Variable</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>CALF, GROWING, CLOSE_UP, LAC_COWS</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -518,12 +515,8 @@
       <c r="C3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -532,12 +525,8 @@
       <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
         <v>12</v>
       </c>
